--- a/设计书.xlsx
+++ b/设计书.xlsx
@@ -4,10 +4,11 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24750" windowHeight="10480"/>
+    <workbookView windowWidth="24750" windowHeight="10480" activeTab="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="RAG" sheetId="1" r:id="rId1"/>
+    <sheet name="handoffs" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -24,6 +25,17 @@
     </ext>
   </extLst>
 </workbook>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
+  <si>
+    <t>main_agent</t>
+  </si>
+  <si>
+    <t>code_agent</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -381,12 +393,92 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="17">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -513,7 +605,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -525,34 +617,34 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -637,8 +729,35 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -5467,6 +5586,3134 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>406400</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>323850</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="圆角矩形 1"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5892800" y="508000"/>
+          <a:ext cx="1136650" cy="558800"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="50000">
+              <a:schemeClr val="accent1"/>
+            </a:gs>
+            <a:gs pos="0">
+              <a:schemeClr val="accent1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="accent1">
+                <a:lumMod val="85000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="1"/>
+        </a:gradFill>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:lumMod val="75000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:srgbClr val="FFFFFF"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr" anchorCtr="0"/>
+        <a:lstStyle>
+          <a:defPPr>
+            <a:defRPr lang="zh-CN">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+            </a:defRPr>
+          </a:defPPr>
+          <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1100"/>
+            <a:t>START</a:t>
+          </a:r>
+          <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>76200</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>82550</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>603250</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>107950</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="圆角矩形 2"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2514600" y="2047875"/>
+          <a:ext cx="1136650" cy="558800"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="50000">
+              <a:schemeClr val="accent1"/>
+            </a:gs>
+            <a:gs pos="0">
+              <a:schemeClr val="accent1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="accent1">
+                <a:lumMod val="85000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="1"/>
+        </a:gradFill>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:lumMod val="75000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:srgbClr val="FFFFFF"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr" anchorCtr="0"/>
+        <a:lstStyle>
+          <a:defPPr>
+            <a:defRPr lang="zh-CN">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+            </a:defRPr>
+          </a:defPPr>
+          <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1100"/>
+            <a:t>START</a:t>
+          </a:r>
+          <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>527050</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>63500</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="4" name="圆角矩形 3"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1219200" y="2892425"/>
+          <a:ext cx="1136650" cy="558800"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="50000">
+              <a:schemeClr val="accent1"/>
+            </a:gs>
+            <a:gs pos="0">
+              <a:schemeClr val="accent1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="accent1">
+                <a:lumMod val="85000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="1"/>
+        </a:gradFill>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:lumMod val="75000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:srgbClr val="FFFFFF"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr" anchorCtr="0"/>
+        <a:lstStyle>
+          <a:defPPr>
+            <a:defRPr lang="zh-CN">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+            </a:defRPr>
+          </a:defPPr>
+          <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1100"/>
+            <a:t>LLM</a:t>
+          </a:r>
+          <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>63500</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>6350</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>590550</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>31750</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5" name="圆角矩形 4"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3111500" y="3394075"/>
+          <a:ext cx="1136650" cy="558800"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="50000">
+              <a:schemeClr val="accent1"/>
+            </a:gs>
+            <a:gs pos="0">
+              <a:schemeClr val="accent1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="accent1">
+                <a:lumMod val="85000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="1"/>
+        </a:gradFill>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:lumMod val="75000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:srgbClr val="FFFFFF"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr" anchorCtr="0"/>
+        <a:lstStyle>
+          <a:defPPr>
+            <a:defRPr lang="zh-CN">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+            </a:defRPr>
+          </a:defPPr>
+          <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1100"/>
+            <a:t>Tools</a:t>
+          </a:r>
+          <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>76200</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>82550</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>603250</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>107950</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="6" name="圆角矩形 5"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9829800" y="2047875"/>
+          <a:ext cx="1136650" cy="558800"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="50000">
+              <a:schemeClr val="accent1"/>
+            </a:gs>
+            <a:gs pos="0">
+              <a:schemeClr val="accent1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="accent1">
+                <a:lumMod val="85000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="1"/>
+        </a:gradFill>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:lumMod val="75000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:srgbClr val="FFFFFF"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr" anchorCtr="0"/>
+        <a:lstStyle>
+          <a:defPPr>
+            <a:defRPr lang="zh-CN">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+            </a:defRPr>
+          </a:defPPr>
+          <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1100"/>
+            <a:t>START</a:t>
+          </a:r>
+          <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>247650</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>12700</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>165100</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="7" name="圆角矩形 6"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10610850" y="3044825"/>
+          <a:ext cx="1136650" cy="558800"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="50000">
+              <a:schemeClr val="accent1"/>
+            </a:gs>
+            <a:gs pos="0">
+              <a:schemeClr val="accent1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="accent1">
+                <a:lumMod val="85000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="1"/>
+        </a:gradFill>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:lumMod val="75000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:srgbClr val="FFFFFF"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr" anchorCtr="0"/>
+        <a:lstStyle>
+          <a:defPPr>
+            <a:defRPr lang="zh-CN">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+            </a:defRPr>
+          </a:defPPr>
+          <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1100"/>
+            <a:t>LLM</a:t>
+          </a:r>
+          <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>546100</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>31750</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>463550</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="8" name="圆角矩形 7"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8470900" y="3241675"/>
+          <a:ext cx="1136650" cy="558800"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="50000">
+              <a:schemeClr val="accent1"/>
+            </a:gs>
+            <a:gs pos="0">
+              <a:schemeClr val="accent1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="accent1">
+                <a:lumMod val="85000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="1"/>
+        </a:gradFill>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:lumMod val="75000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:srgbClr val="FFFFFF"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr" anchorCtr="0"/>
+        <a:lstStyle>
+          <a:defPPr>
+            <a:defRPr lang="zh-CN">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+            </a:defRPr>
+          </a:defPPr>
+          <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1100"/>
+            <a:t>Tools</a:t>
+          </a:r>
+          <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>34925</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>406400</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>82550</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp>
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="9" name="曲线连接符 8"/>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="2" idx="1"/>
+          <a:endCxn id="3" idx="0"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="10800000" flipV="1">
+          <a:off x="3082925" y="787400"/>
+          <a:ext cx="2809875" cy="1260475"/>
+        </a:xfrm>
+        <a:prstGeom prst="curvedConnector2">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="arrow"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:srgbClr val="FFFFFF"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:srgbClr val="FFFFFF"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>567690</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>6350</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>75565</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp>
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="10" name="曲线连接符 9"/>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="3" idx="1"/>
+          <a:endCxn id="4" idx="0"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="10800000" flipV="1">
+          <a:off x="1786890" y="2327275"/>
+          <a:ext cx="727075" cy="565150"/>
+        </a:xfrm>
+        <a:prstGeom prst="curvedConnector2">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="arrow"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:srgbClr val="FFFFFF"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:srgbClr val="FFFFFF"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>527050</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>139700</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>22225</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>6350</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp>
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="11" name="曲线连接符 10"/>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="4" idx="3"/>
+          <a:endCxn id="5" idx="0"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2355850" y="3171825"/>
+          <a:ext cx="1323975" cy="222250"/>
+        </a:xfrm>
+        <a:prstGeom prst="curvedConnector2">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="arrow"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:srgbClr val="FFFFFF"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:srgbClr val="FFFFFF"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>450850</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>63500</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>368300</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>88900</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="12" name="圆角矩形 11"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1060450" y="4162425"/>
+          <a:ext cx="1136650" cy="558800"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="50000">
+              <a:schemeClr val="accent1"/>
+            </a:gs>
+            <a:gs pos="0">
+              <a:schemeClr val="accent1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="accent1">
+                <a:lumMod val="85000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="1"/>
+        </a:gradFill>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:lumMod val="75000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:srgbClr val="FFFFFF"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr" anchorCtr="0"/>
+        <a:lstStyle>
+          <a:defPPr>
+            <a:defRPr lang="zh-CN">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+            </a:defRPr>
+          </a:defPPr>
+          <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1100"/>
+            <a:t>END</a:t>
+          </a:r>
+          <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>425450</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>12700</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>342900</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="13" name="圆角矩形 12"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10788650" y="4111625"/>
+          <a:ext cx="1136650" cy="558800"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="50000">
+              <a:schemeClr val="accent1"/>
+            </a:gs>
+            <a:gs pos="0">
+              <a:schemeClr val="accent1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="accent1">
+                <a:lumMod val="85000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="1"/>
+        </a:gradFill>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:lumMod val="75000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:srgbClr val="FFFFFF"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr" anchorCtr="0"/>
+        <a:lstStyle>
+          <a:defPPr>
+            <a:defRPr lang="zh-CN">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+            </a:defRPr>
+          </a:defPPr>
+          <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1100"/>
+            <a:t>END</a:t>
+          </a:r>
+          <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>568325</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>63500</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>22225</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>31750</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp>
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="14" name="曲线连接符 13"/>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="5" idx="2"/>
+          <a:endCxn id="4" idx="2"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="5400000" flipH="1">
+          <a:off x="2482850" y="2755900"/>
+          <a:ext cx="501650" cy="1892300"/>
+        </a:xfrm>
+        <a:prstGeom prst="curvedConnector3">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val -47468"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="arrow"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:srgbClr val="FFFFFF"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:srgbClr val="FFFFFF"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>450850</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>139700</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>165100</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp>
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="15" name="曲线连接符 14"/>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="4" idx="1"/>
+          <a:endCxn id="12" idx="1"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="10800000" flipV="1">
+          <a:off x="1060450" y="3171825"/>
+          <a:ext cx="158750" cy="1270000"/>
+        </a:xfrm>
+        <a:prstGeom prst="curvedConnector3">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val 250000"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="arrow"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:srgbClr val="FFFFFF"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:srgbClr val="FFFFFF"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>590550</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>6350</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>76200</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>107950</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp>
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="16" name="曲线连接符 15"/>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="5" idx="3"/>
+          <a:endCxn id="6" idx="1"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="4248150" y="2327275"/>
+          <a:ext cx="5581650" cy="1346200"/>
+        </a:xfrm>
+        <a:prstGeom prst="curvedConnector3">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val 50000"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="arrow"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:srgbClr val="FFFFFF"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:srgbClr val="FFFFFF"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>400050</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>63500</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>317500</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>88900</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="17" name="圆角矩形 16"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5886450" y="5238750"/>
+          <a:ext cx="1136650" cy="558800"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="50000">
+              <a:schemeClr val="accent1"/>
+            </a:gs>
+            <a:gs pos="0">
+              <a:schemeClr val="accent1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="accent1">
+                <a:lumMod val="85000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="1"/>
+        </a:gradFill>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:lumMod val="75000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:srgbClr val="FFFFFF"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr" anchorCtr="0"/>
+        <a:lstStyle>
+          <a:defPPr>
+            <a:defRPr lang="zh-CN">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+            </a:defRPr>
+          </a:defPPr>
+          <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1100"/>
+            <a:t>END</a:t>
+          </a:r>
+          <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>323850</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>34925</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>82550</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp>
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="18" name="曲线连接符 17"/>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="2" idx="3"/>
+          <a:endCxn id="6" idx="0"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7029450" y="787400"/>
+          <a:ext cx="3368675" cy="1260475"/>
+        </a:xfrm>
+        <a:prstGeom prst="curvedConnector2">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="arrow"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:srgbClr val="FFFFFF"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:srgbClr val="FFFFFF"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>285750</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>6985</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>25400</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="19" name="文本框 18"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3943350" y="806450"/>
+          <a:ext cx="940435" cy="285750"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="en-US" sz="1100"/>
+            <a:t>route_initial</a:t>
+          </a:r>
+          <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>457200</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>6350</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>178435</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="20" name="文本框 19"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7772400" y="717550"/>
+          <a:ext cx="940435" cy="285750"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle>
+          <a:defPPr>
+            <a:defRPr lang="zh-CN">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+            </a:defRPr>
+          </a:defPPr>
+          <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="en-US" sz="1100"/>
+            <a:t>route_initial</a:t>
+          </a:r>
+          <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>368300</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>165100</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>400050</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>165100</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp>
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="21" name="曲线连接符 20"/>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="12" idx="3"/>
+          <a:endCxn id="17" idx="1"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2197100" y="4441825"/>
+          <a:ext cx="3689350" cy="1076325"/>
+        </a:xfrm>
+        <a:prstGeom prst="curvedConnector3">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val 50000"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="arrow"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:srgbClr val="FFFFFF"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:srgbClr val="FFFFFF"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>317500</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>425450</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>165100</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp>
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="22" name="曲线连接符 21"/>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="13" idx="1"/>
+          <a:endCxn id="17" idx="3"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="10800000" flipV="1">
+          <a:off x="7023100" y="4391025"/>
+          <a:ext cx="3765550" cy="1127125"/>
+        </a:xfrm>
+        <a:prstGeom prst="curvedConnector3">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val 50000"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="arrow"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:srgbClr val="FFFFFF"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:srgbClr val="FFFFFF"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>34925</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>107950</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>206375</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>12700</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp>
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="23" name="曲线连接符 22"/>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="6" idx="2"/>
+          <a:endCxn id="7" idx="0"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="5400000" flipV="1">
+          <a:off x="10569575" y="2435225"/>
+          <a:ext cx="438150" cy="781050"/>
+        </a:xfrm>
+        <a:prstGeom prst="curvedConnector3">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val 50000"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="arrow"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:srgbClr val="FFFFFF"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:srgbClr val="FFFFFF"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>504825</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>31750</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>247650</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp>
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="24" name="曲线连接符 23"/>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="7" idx="1"/>
+          <a:endCxn id="8" idx="0"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="10800000">
+          <a:off x="9039225" y="3241675"/>
+          <a:ext cx="1571625" cy="82550"/>
+        </a:xfrm>
+        <a:prstGeom prst="curvedConnector4">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val 31919"/>
+            <a:gd name="adj2" fmla="val 626923"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="arrow"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:srgbClr val="FFFFFF"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:srgbClr val="FFFFFF"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>603250</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>6350</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>546100</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp>
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="25" name="曲线连接符 24"/>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="8" idx="1"/>
+          <a:endCxn id="3" idx="3"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="10800000">
+          <a:off x="3651250" y="2327275"/>
+          <a:ext cx="4819650" cy="1193800"/>
+        </a:xfrm>
+        <a:prstGeom prst="curvedConnector3">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val 50000"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="arrow"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:srgbClr val="FFFFFF"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:srgbClr val="FFFFFF"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>463550</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>206375</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp>
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="26" name="曲线连接符 25"/>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="8" idx="3"/>
+          <a:endCxn id="7" idx="2"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9607550" y="3521075"/>
+          <a:ext cx="1571625" cy="82550"/>
+        </a:xfrm>
+        <a:prstGeom prst="curvedConnector4">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val 31919"/>
+            <a:gd name="adj2" fmla="val 626923"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="arrow"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:srgbClr val="FFFFFF"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:srgbClr val="FFFFFF"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>165100</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>342900</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp>
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="27" name="曲线连接符 26"/>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="7" idx="3"/>
+          <a:endCxn id="13" idx="3"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11747500" y="3324225"/>
+          <a:ext cx="177800" cy="1066800"/>
+        </a:xfrm>
+        <a:prstGeom prst="curvedConnector3">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val 233929"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="arrow"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:srgbClr val="FFFFFF"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:srgbClr val="FFFFFF"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>184150</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>513715</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>50800</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="28" name="文本框 27"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4451350" y="3324225"/>
+          <a:ext cx="939165" cy="469900"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle>
+          <a:defPPr>
+            <a:defRPr lang="zh-CN">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+            </a:defRPr>
+          </a:defPPr>
+          <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="en-US" sz="1100"/>
+            <a:t>transfer_to_code_agent</a:t>
+          </a:r>
+          <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>578485</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>299085</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>107950</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="29" name="文本框 28"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7284085" y="3203575"/>
+          <a:ext cx="939800" cy="469900"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle>
+          <a:defPPr>
+            <a:defRPr lang="zh-CN">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+            </a:defRPr>
+          </a:defPPr>
+          <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="en-US" sz="1100"/>
+            <a:t>transfer_to_main_agent</a:t>
+          </a:r>
+          <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="WPS">
   <a:themeElements>
@@ -5724,4 +8971,154 @@
   <headerFooter/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="B8:T27"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14"/>
+  <sheetData>
+    <row r="8" spans="2:20">
+      <c r="C8" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="S8" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" ht="14.75"/>
+    <row r="10" spans="2:20">
+      <c r="B10" s="2"/>
+      <c r="C10" s="3"/>
+      <c r="D10" s="3"/>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3"/>
+      <c r="G10" s="3"/>
+      <c r="H10" s="4"/>
+      <c r="N10" s="2"/>
+      <c r="O10" s="3"/>
+      <c r="P10" s="3"/>
+      <c r="Q10" s="3"/>
+      <c r="R10" s="3"/>
+      <c r="S10" s="3"/>
+      <c r="T10" s="4"/>
+    </row>
+    <row r="11" spans="2:20">
+      <c r="B11" s="5"/>
+      <c r="H11" s="6"/>
+      <c r="N11" s="5"/>
+      <c r="T11" s="6"/>
+    </row>
+    <row r="12" spans="2:20">
+      <c r="B12" s="5"/>
+      <c r="H12" s="6"/>
+      <c r="N12" s="5"/>
+      <c r="T12" s="6"/>
+    </row>
+    <row r="13" spans="2:20">
+      <c r="B13" s="5"/>
+      <c r="H13" s="6"/>
+      <c r="N13" s="5"/>
+      <c r="T13" s="6"/>
+    </row>
+    <row r="14" spans="2:20">
+      <c r="B14" s="5"/>
+      <c r="H14" s="6"/>
+      <c r="N14" s="5"/>
+      <c r="T14" s="6"/>
+    </row>
+    <row r="15" spans="2:20">
+      <c r="B15" s="5"/>
+      <c r="H15" s="6"/>
+      <c r="N15" s="5"/>
+      <c r="T15" s="6"/>
+    </row>
+    <row r="16" spans="2:20">
+      <c r="B16" s="5"/>
+      <c r="H16" s="6"/>
+      <c r="N16" s="5"/>
+      <c r="T16" s="6"/>
+    </row>
+    <row r="17" spans="2:20">
+      <c r="B17" s="5"/>
+      <c r="H17" s="6"/>
+      <c r="N17" s="5"/>
+      <c r="T17" s="6"/>
+    </row>
+    <row r="18" spans="2:20">
+      <c r="B18" s="5"/>
+      <c r="H18" s="6"/>
+      <c r="N18" s="5"/>
+      <c r="T18" s="6"/>
+    </row>
+    <row r="19" spans="2:20">
+      <c r="B19" s="5"/>
+      <c r="H19" s="6"/>
+      <c r="N19" s="5"/>
+      <c r="T19" s="6"/>
+    </row>
+    <row r="20" spans="2:20">
+      <c r="B20" s="5"/>
+      <c r="H20" s="6"/>
+      <c r="N20" s="5"/>
+      <c r="T20" s="6"/>
+    </row>
+    <row r="21" spans="2:20">
+      <c r="B21" s="5"/>
+      <c r="H21" s="6"/>
+      <c r="N21" s="5"/>
+      <c r="T21" s="6"/>
+    </row>
+    <row r="22" spans="2:20">
+      <c r="B22" s="5"/>
+      <c r="H22" s="6"/>
+      <c r="N22" s="5"/>
+      <c r="T22" s="6"/>
+    </row>
+    <row r="23" spans="2:20">
+      <c r="B23" s="5"/>
+      <c r="H23" s="6"/>
+      <c r="N23" s="5"/>
+      <c r="T23" s="6"/>
+    </row>
+    <row r="24" spans="2:20">
+      <c r="B24" s="5"/>
+      <c r="H24" s="6"/>
+      <c r="N24" s="5"/>
+      <c r="T24" s="6"/>
+    </row>
+    <row r="25" spans="2:20">
+      <c r="B25" s="5"/>
+      <c r="H25" s="6"/>
+      <c r="N25" s="5"/>
+      <c r="T25" s="6"/>
+    </row>
+    <row r="26" spans="2:20">
+      <c r="B26" s="5"/>
+      <c r="H26" s="6"/>
+      <c r="N26" s="5"/>
+      <c r="T26" s="6"/>
+    </row>
+    <row r="27" ht="14.75" spans="2:20">
+      <c r="B27" s="7"/>
+      <c r="C27" s="8"/>
+      <c r="D27" s="8"/>
+      <c r="E27" s="8"/>
+      <c r="F27" s="8"/>
+      <c r="G27" s="8"/>
+      <c r="H27" s="9"/>
+      <c r="N27" s="7"/>
+      <c r="O27" s="8"/>
+      <c r="P27" s="8"/>
+      <c r="Q27" s="8"/>
+      <c r="R27" s="8"/>
+      <c r="S27" s="8"/>
+      <c r="T27" s="9"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>
--- a/设计书.xlsx
+++ b/设计书.xlsx
@@ -1,16 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24334"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\seki\AI\Langchain\SIS_Agent\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{AA92567B-54EC-4E7D-A9AF-25AD6993DB3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="24750" windowHeight="10480" activeTab="1"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="RAG" sheetId="1" r:id="rId1"/>
-    <sheet name="handoffs" sheetId="2" r:id="rId2"/>
+    <sheet name="整体架构" sheetId="3" r:id="rId1"/>
+    <sheet name="skills" sheetId="5" r:id="rId2"/>
+    <sheet name="文档翻译" sheetId="4" r:id="rId3"/>
+    <sheet name="RAG" sheetId="1" r:id="rId4"/>
+    <sheet name="handoffs" sheetId="2" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -19,34 +29,177 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="39">
   <si>
     <t>main_agent</t>
   </si>
   <si>
     <t>code_agent</t>
   </si>
+  <si>
+    <t>课题</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.memory</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>长期记忆</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>2.RAG优化</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>已完成</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>评估体系（如用RAGAS评估检索质量）</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>3.prompt优化</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>4.思考过程优化</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>5.subagent</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>6.MCP</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>7.multiagent</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>8.UI</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>9.响应速度优化</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>10.翻译工具改进：1.多模型并行翻译，提高大文件翻译效率2.引入图片处理大模型，优化ppt视觉效果3.定期写入文件，防止大文件最后功亏一篑</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>11.控制台打印信息显示在前端</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>12.agent可操作cli，能自己写简单工具</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>学习使用 loguru 或 logging 替换 print</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>学习 astream_events 替代手工状态解析</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>尝试构建多Agent协作（例如一个Agent负责检索，另一个Agent负责验证答案）</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>RAG进阶技巧</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>实现 HyDE（假设性文档嵌入）或 Query2Doc</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>添加 Self-RAG 或 CRAG（修正检索）</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>部署与运维</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>将Agent封装成FastAPI服务，并提供Dockerfile</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>学习使用 langsmith 或 langfuse 做trace和评估</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>ToDo List</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.Claude code同款双重验证机制（token消耗+最大循环数）</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>2.操控CLI的subagent</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>沙箱环境，工具，提示词优化</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>3.FastAPI</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>4.长期记忆</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>5.RAG评估</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>6.强制打断对话</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>7.多轮对话</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>8.实现闪客的上下文选择删除功能和费用输出</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>9.制作PPT的skill</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>10.父子检索无法召回的bug</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="20">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -55,345 +208,44 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <strike/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="17">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -481,255 +333,14 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -760,90 +371,163 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+    <cellStyle name="常规 2" xfId="1" xr:uid="{F1C06CC9-BBD5-4F4B-AFF9-65124599EE34}"/>
   </cellStyles>
   <dxfs count="17">
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
+        <b/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+      <border>
+        <top style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
         <color theme="1"/>
       </font>
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
+        <b/>
         <color theme="1"/>
       </font>
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
+        <b/>
         <color theme="1"/>
       </font>
       <border>
@@ -854,7 +538,7 @@
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
+        <b/>
         <color theme="0"/>
       </font>
       <fill>
@@ -882,161 +566,1885 @@
           <color theme="4"/>
         </bottom>
         <horizontal style="thin">
-          <color theme="4" tint="0.399975585192419"/>
+          <color theme="4" tint="0.39994506668294322"/>
         </horizontal>
       </border>
     </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <border>
-        <top style="thin">
-          <color theme="4"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <top style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
   </dxfs>
-  <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
+  <tableStyles count="2" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
     <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
-      <tableStyleElement type="wholeTable" dxfId="6"/>
-      <tableStyleElement type="headerRow" dxfId="5"/>
-      <tableStyleElement type="totalRow" dxfId="4"/>
-      <tableStyleElement type="firstColumn" dxfId="3"/>
-      <tableStyleElement type="lastColumn" dxfId="2"/>
-      <tableStyleElement type="firstRowStripe" dxfId="1"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="0"/>
+      <tableStyleElement type="wholeTable" dxfId="16"/>
+      <tableStyleElement type="headerRow" dxfId="15"/>
+      <tableStyleElement type="totalRow" dxfId="14"/>
+      <tableStyleElement type="firstColumn" dxfId="13"/>
+      <tableStyleElement type="lastColumn" dxfId="12"/>
+      <tableStyleElement type="firstRowStripe" dxfId="11"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="10"/>
     </tableStyle>
     <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
-      <tableStyleElement type="headerRow" dxfId="16"/>
-      <tableStyleElement type="totalRow" dxfId="15"/>
-      <tableStyleElement type="firstRowStripe" dxfId="14"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="13"/>
-      <tableStyleElement type="firstSubtotalRow" dxfId="12"/>
-      <tableStyleElement type="secondSubtotalRow" dxfId="11"/>
-      <tableStyleElement type="firstRowSubheading" dxfId="10"/>
-      <tableStyleElement type="secondRowSubheading" dxfId="9"/>
-      <tableStyleElement type="pageFieldLabels" dxfId="8"/>
-      <tableStyleElement type="pageFieldValues" dxfId="7"/>
+      <tableStyleElement type="headerRow" dxfId="9"/>
+      <tableStyleElement type="totalRow" dxfId="8"/>
+      <tableStyleElement type="firstRowStripe" dxfId="7"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="6"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="5"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="4"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="3"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="2"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="1"/>
+      <tableStyleElement type="pageFieldValues" dxfId="0"/>
     </tableStyle>
   </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
   </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>198530</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>112059</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>444313</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>100292</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="矩形: 圆角 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3C88C495-2454-48AC-B28C-5965ED17FE7F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5039471" y="2084294"/>
+          <a:ext cx="1456018" cy="884704"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1400"/>
+            <a:t>main_agent</a:t>
+          </a:r>
+          <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1400"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>29</xdr:col>
+      <xdr:colOff>324595</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>15688</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>29</xdr:col>
+      <xdr:colOff>351116</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>134471</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="4" name="直接连接符 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1E668A1D-45BF-4E65-A36F-3ABD07A2E825}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:cxnSpLocks/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="17873007" y="912159"/>
+          <a:ext cx="26521" cy="835959"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>296956</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>18116</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>201705</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>18116</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="6" name="直接连接符 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{19E4032B-DAC3-4B91-98DC-8424AC783321}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:cxnSpLocks/>
+          <a:stCxn id="55" idx="3"/>
+          <a:endCxn id="2" idx="1"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3927662" y="2528234"/>
+          <a:ext cx="1114984" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>87406</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>69477</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>268941</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>69476</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="8" name="矩形: 圆角 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1AFE26AD-B2E0-4EA8-9FD3-98ED9B8A898D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="692524" y="5089712"/>
+          <a:ext cx="1391770" cy="717176"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1200"/>
+            <a:t>Tool1</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="en-US" sz="1200"/>
+            <a:t>：文档翻译</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>178175</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>103467</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>324597</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>69477</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="9" name="连接符: 肘形 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{951E2695-828F-4CB2-8A89-5E30A86A78BD}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="8" idx="0"/>
+          <a:endCxn id="2" idx="2"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="5400000" flipH="1" flipV="1">
+          <a:off x="2520763" y="1839820"/>
+          <a:ext cx="2117539" cy="4382246"/>
+        </a:xfrm>
+        <a:prstGeom prst="bentConnector3">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>95250</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>1681</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>324971</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>1681</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="12" name="矩形 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6B749764-AA10-4DE9-98F0-96EC9395B7A6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="95250" y="3228975"/>
+          <a:ext cx="9911603" cy="5378824"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="28575"/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1100" b="1" cap="none" spc="0">
+            <a:ln w="22225">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+            <a:solidFill>
+              <a:schemeClr val="accent2">
+                <a:lumMod val="40000"/>
+                <a:lumOff val="60000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>323850</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>142875</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>619125</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>44450</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="13" name="文本框 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E598BC93-8A40-4F24-A869-4B021FD29EC7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2295525" y="3397250"/>
+          <a:ext cx="949325" cy="269875"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1600"/>
+            <a:t>Tools</a:t>
+          </a:r>
+          <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1600"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>421342</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>29508</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>183217</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>107201</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="14" name="矩形: 圆角 13">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2C39E651-1DA5-4BA4-8849-D0A09612452A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5262283" y="5049743"/>
+          <a:ext cx="1577228" cy="794870"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1200"/>
+            <a:t>Tool3</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="en-US" sz="1200"/>
+            <a:t>：联网检索</a:t>
+          </a:r>
+          <a:br>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1200"/>
+          </a:br>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="en-US" sz="1200"/>
+            <a:t>（基于火山引擎搜索工具）</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>324597</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>103467</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>603252</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>26333</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="15" name="连接符: 肘形 14">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{37EF266C-1EA4-47D0-A023-CD56820B8FD2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="14" idx="0"/>
+          <a:endCxn id="2" idx="2"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="16200000" flipV="1">
+          <a:off x="4872786" y="3870043"/>
+          <a:ext cx="2074395" cy="278655"/>
+        </a:xfrm>
+        <a:prstGeom prst="bentConnector3">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val 50000"/>
+          </a:avLst>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>181535</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>19797</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>603810</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>84790</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="18" name="矩形: 圆角 17">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{04C91FF7-AE79-4763-B343-ECA18F5164E0}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2602006" y="5040032"/>
+          <a:ext cx="1632510" cy="782170"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1200"/>
+            <a:t>Tool2</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="en-US" sz="1200"/>
+            <a:t>：</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1200"/>
+            <a:t>RAG</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="en-US" sz="1200"/>
+            <a:t>本地知识库检索</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>588308</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>16435</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>347008</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>84603</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="20" name="矩形: 圆角 19">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5819D18C-B2D2-432F-9A46-802ADBC26787}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7849720" y="5036670"/>
+          <a:ext cx="1574053" cy="785345"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1200"/>
+            <a:t>Tool4</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="en-US" sz="1200"/>
+            <a:t>：交接工具</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>324597</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>103467</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>166688</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>16435</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="21" name="连接符: 肘形 20">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9BFECBCF-FD55-4CA6-B158-C2611B039C85}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="20" idx="0"/>
+          <a:endCxn id="2" idx="2"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="16200000" flipV="1">
+          <a:off x="6172247" y="2570582"/>
+          <a:ext cx="2064497" cy="2867679"/>
+        </a:xfrm>
+        <a:prstGeom prst="bentConnector3">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val 50000"/>
+          </a:avLst>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>107391</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>258482</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>108324</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="45" name="矩形: 圆角 44">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B2546A9D-BDAB-41CF-9C99-568B7384FAF6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="13312588" y="2079626"/>
+          <a:ext cx="1468718" cy="897404"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1400"/>
+            <a:t>code_agent</a:t>
+          </a:r>
+          <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1400"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>115234</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>47998</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>370542</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>39406</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="46" name="矩形: 圆角 45">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1BF14AA2-AC59-4598-876E-EC91C755E157}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8586881" y="406586"/>
+          <a:ext cx="1465543" cy="887879"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1400"/>
+            <a:t>user</a:t>
+          </a:r>
+          <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1400"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>324596</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>39407</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>244475</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>112060</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="47" name="连接符: 肘形 46">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7722EE32-DA96-45C4-9523-B5359BD7ABC8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="2" idx="0"/>
+          <a:endCxn id="46" idx="2"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="5400000" flipH="1" flipV="1">
+          <a:off x="7151033" y="-85912"/>
+          <a:ext cx="789829" cy="3550585"/>
+        </a:xfrm>
+        <a:prstGeom prst="bentConnector3">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val 50000"/>
+          </a:avLst>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>244475</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>39406</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>127654</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>104216</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="52" name="连接符: 肘形 51">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{31855D57-255C-4BBE-9560-DD1B07FD4E47}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="45" idx="0"/>
+          <a:endCxn id="46" idx="2"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="16200000" flipV="1">
+          <a:off x="11292307" y="-676602"/>
+          <a:ext cx="781986" cy="4724120"/>
+        </a:xfrm>
+        <a:prstGeom prst="bentConnector3">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val 50000"/>
+          </a:avLst>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>44823</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>112059</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>300131</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>106642</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="55" name="矩形: 圆角 54">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FF13FB69-E425-4328-B954-19233C10F5F9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2465294" y="2084294"/>
+          <a:ext cx="1465543" cy="891054"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>LLM</a:t>
+          </a:r>
+          <a:endParaRPr lang="zh-CN" altLang="zh-CN" sz="1400">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="zh-CN" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>（千问</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>3.5plus</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="zh-CN" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>）</a:t>
+          </a:r>
+          <a:endParaRPr lang="zh-CN" altLang="zh-CN" sz="1400">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>255307</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>466</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>27</xdr:col>
+      <xdr:colOff>372970</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>15035</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="58" name="直接连接符 57">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CC2B7E12-7D45-448B-9A22-944742D2BCA2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:cxnSpLocks/>
+          <a:stCxn id="59" idx="1"/>
+          <a:endCxn id="45" idx="3"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="14778131" y="2510584"/>
+          <a:ext cx="1933015" cy="14569"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>27</xdr:col>
+      <xdr:colOff>369795</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>92822</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>30</xdr:col>
+      <xdr:colOff>7285</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>84230</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="59" name="矩形: 圆角 58">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8F0FB7EB-9FEE-46C9-8ACB-EB8EB4832F24}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="16707971" y="2065057"/>
+          <a:ext cx="1452843" cy="887879"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>LLM</a:t>
+          </a:r>
+          <a:endParaRPr lang="zh-CN" altLang="zh-CN" sz="1400">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="zh-CN" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>（千问</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>3.5plus</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="zh-CN" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>）</a:t>
+          </a:r>
+          <a:endParaRPr lang="zh-CN" altLang="zh-CN" sz="1400">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>389498</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>103468</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>324596</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>19798</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="67" name="连接符: 肘形 66">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{47E52CA8-466E-48D4-A4DE-41CD2AE52818}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="18" idx="0"/>
+          <a:endCxn id="2" idx="2"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="5400000" flipH="1" flipV="1">
+          <a:off x="3558941" y="2828319"/>
+          <a:ext cx="2067859" cy="2355569"/>
+        </a:xfrm>
+        <a:prstGeom prst="bentConnector3">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val 50000"/>
+          </a:avLst>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>353733</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>30</xdr:col>
+      <xdr:colOff>296957</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="77" name="矩形 76">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5FA0FBE1-D0B3-4C63-B09E-657C3A69178C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11245851" y="3227294"/>
+          <a:ext cx="7204635" cy="5378824"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="28575"/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1100" b="1" cap="none" spc="0">
+            <a:ln w="22225">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+            <a:solidFill>
+              <a:schemeClr val="accent2">
+                <a:lumMod val="40000"/>
+                <a:lumOff val="60000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>156883</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>100853</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>530225</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>165847</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="81" name="矩形: 圆角 80">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9410D008-B898-4D6F-8B44-5E8DDDF996A7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11654118" y="4583206"/>
+          <a:ext cx="1583578" cy="782170"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1200"/>
+            <a:t>Tool4</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="en-US" sz="1200"/>
+            <a:t>：读文件</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>381000</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>145676</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>146050</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>15500</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="82" name="矩形: 圆角 81">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{23A216CC-F7B1-409C-8A39-9A53E7C62323}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="13693588" y="4628029"/>
+          <a:ext cx="1580403" cy="766295"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1200"/>
+            <a:t>Tool4</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="en-US" sz="1200"/>
+            <a:t>：读文件</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>59578</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>305920</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>132790</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="2" name="连接符: 肘形 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A3321D19-E8C6-4F18-9BAF-5C4A79224C81}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="3" idx="0"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="16200000" flipV="1">
+          <a:off x="3626316" y="3167437"/>
+          <a:ext cx="1037665" cy="855942"/>
+        </a:xfrm>
+        <a:prstGeom prst="bentConnector3">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val 50000"/>
+          </a:avLst>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>186578</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>132790</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>411256</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>30816</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="矩形: 圆角 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5C0FD054-6BD4-4FB1-BDCA-26849620FAD5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3844178" y="4114240"/>
+          <a:ext cx="1443878" cy="802901"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="en-US" sz="1200"/>
+            <a:t>翻译模型：千问</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1200"/>
+            <a:t>plus</a:t>
+          </a:r>
+          <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1200"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>135965</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>359335</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>146610</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="4" name="矩形: 圆角 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AE1328B6-DE8D-4B26-BBB6-6A3F03C28830}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1828800" y="4117415"/>
+          <a:ext cx="1578535" cy="915520"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="en-US" sz="900" baseline="0"/>
+            <a:t>支持文档：</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" altLang="zh-CN" sz="900" baseline="0"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="900" baseline="0"/>
+            <a:t>Excel</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="en-US" sz="900" baseline="0"/>
+            <a:t>（多线程）</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" altLang="zh-CN" sz="900" baseline="0"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="900" baseline="0"/>
+            <a:t>PPT</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="en-US" sz="900" baseline="0"/>
+            <a:t>（多线程）</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" altLang="zh-CN" sz="900" baseline="0"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="900" baseline="0"/>
+            <a:t>Worf</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="en-US" sz="900" baseline="0"/>
+            <a:t>（单线程）</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>178081</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>59579</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>135965</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="5" name="连接符: 肘形 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6F42A332-FD5D-4831-894C-518133B7FEE2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="4" idx="0"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="5400000" flipH="1" flipV="1">
+          <a:off x="2646410" y="3046646"/>
+          <a:ext cx="1040840" cy="1100698"/>
+        </a:xfrm>
+        <a:prstGeom prst="bentConnector3">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val 50000"/>
+          </a:avLst>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>3</xdr:col>
@@ -1050,9 +2458,15 @@
       <xdr:row>6</xdr:row>
       <xdr:rowOff>12700</xdr:rowOff>
     </xdr:to>
-    <xdr:sp>
+    <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="2" name="圆角矩形 1"/>
+        <xdr:cNvPr id="2" name="圆角矩形 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -1082,15 +2496,6 @@
           </a:gsLst>
           <a:lin ang="5400000" scaled="1"/>
         </a:gradFill>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
       </xdr:spPr>
       <xdr:style>
         <a:lnRef idx="2">
@@ -1110,13 +2515,13 @@
       </xdr:style>
       <xdr:txBody>
         <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr" anchorCtr="0"/>
+        <a:lstStyle/>
         <a:p>
           <a:pPr algn="ctr"/>
           <a:r>
             <a:rPr lang="zh-CN" altLang="en-US" sz="1100"/>
             <a:t>本地文档</a:t>
           </a:r>
-          <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1100"/>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -1135,9 +2540,15 @@
       <xdr:row>3</xdr:row>
       <xdr:rowOff>127000</xdr:rowOff>
     </xdr:to>
-    <xdr:sp>
+    <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="3" name="圆角矩形 2"/>
+        <xdr:cNvPr id="3" name="圆角矩形 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000003000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -1167,15 +2578,6 @@
           </a:gsLst>
           <a:lin ang="5400000" scaled="1"/>
         </a:gradFill>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
       </xdr:spPr>
       <xdr:style>
         <a:lnRef idx="2">
@@ -1300,7 +2702,6 @@
             <a:rPr lang="zh-CN" altLang="en-US" sz="1100"/>
             <a:t>用户</a:t>
           </a:r>
-          <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1100"/>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -1319,9 +2720,15 @@
       <xdr:row>13</xdr:row>
       <xdr:rowOff>171450</xdr:rowOff>
     </xdr:to>
-    <xdr:sp>
+    <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="4" name="圆角矩形 3"/>
+        <xdr:cNvPr id="4" name="圆角矩形 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000004000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -1351,15 +2758,6 @@
           </a:gsLst>
           <a:lin ang="5400000" scaled="1"/>
         </a:gradFill>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
       </xdr:spPr>
       <xdr:style>
         <a:lnRef idx="2">
@@ -1503,9 +2901,15 @@
       <xdr:row>13</xdr:row>
       <xdr:rowOff>171450</xdr:rowOff>
     </xdr:to>
-    <xdr:sp>
+    <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="5" name="圆角矩形 4"/>
+        <xdr:cNvPr id="5" name="圆角矩形 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000005000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -1535,15 +2939,6 @@
           </a:gsLst>
           <a:lin ang="5400000" scaled="1"/>
         </a:gradFill>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
       </xdr:spPr>
       <xdr:style>
         <a:lnRef idx="2">
@@ -1668,7 +3063,6 @@
             <a:rPr lang="en-US" altLang="zh-CN" sz="1100"/>
             <a:t>LLM</a:t>
           </a:r>
-          <a:endParaRPr lang="en-US" altLang="zh-CN" sz="1100"/>
         </a:p>
         <a:p>
           <a:pPr algn="ctr"/>
@@ -1676,7 +3070,6 @@
             <a:rPr lang="zh-CN" altLang="en-US" sz="1100"/>
             <a:t>（qwen3.5-plus）</a:t>
           </a:r>
-          <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1100"/>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -1695,9 +3088,15 @@
       <xdr:row>25</xdr:row>
       <xdr:rowOff>95885</xdr:rowOff>
     </xdr:to>
-    <xdr:sp>
+    <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="6" name="圆角矩形 5"/>
+        <xdr:cNvPr id="6" name="圆角矩形 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000006000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -1727,15 +3126,6 @@
           </a:gsLst>
           <a:lin ang="5400000" scaled="1"/>
         </a:gradFill>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
       </xdr:spPr>
       <xdr:style>
         <a:lnRef idx="2">
@@ -1860,7 +3250,6 @@
             <a:rPr lang="zh-CN" altLang="en-US" sz="1100"/>
             <a:t>父文档</a:t>
           </a:r>
-          <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1100"/>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -1879,9 +3268,15 @@
       <xdr:row>25</xdr:row>
       <xdr:rowOff>69850</xdr:rowOff>
     </xdr:to>
-    <xdr:sp>
+    <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="7" name="圆角矩形 6"/>
+        <xdr:cNvPr id="7" name="圆角矩形 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000007000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -1911,15 +3306,6 @@
           </a:gsLst>
           <a:lin ang="5400000" scaled="1"/>
         </a:gradFill>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
       </xdr:spPr>
       <xdr:style>
         <a:lnRef idx="2">
@@ -2044,7 +3430,6 @@
             <a:rPr lang="zh-CN" altLang="en-US" sz="1100"/>
             <a:t>向量库</a:t>
           </a:r>
-          <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1100"/>
         </a:p>
         <a:p>
           <a:pPr algn="ctr"/>
@@ -2060,7 +3445,6 @@
             <a:rPr lang="zh-CN" altLang="en-US" sz="1100"/>
             <a:t>）</a:t>
           </a:r>
-          <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1100"/>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -2079,9 +3463,15 @@
       <xdr:row>10</xdr:row>
       <xdr:rowOff>62865</xdr:rowOff>
     </xdr:to>
-    <xdr:sp>
+    <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="8" name="圆角矩形 7"/>
+        <xdr:cNvPr id="8" name="圆角矩形 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000008000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -2111,15 +3501,6 @@
           </a:gsLst>
           <a:lin ang="5400000" scaled="1"/>
         </a:gradFill>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
       </xdr:spPr>
       <xdr:style>
         <a:lnRef idx="2">
@@ -2248,7 +3629,6 @@
             <a:rPr lang="en-US" altLang="zh-CN" sz="1100"/>
             <a:t>LLM</a:t>
           </a:r>
-          <a:endParaRPr lang="en-US" altLang="zh-CN" sz="1100"/>
         </a:p>
         <a:p>
           <a:pPr algn="ctr"/>
@@ -2256,7 +3636,6 @@
             <a:rPr lang="zh-CN" altLang="en-US" sz="1100"/>
             <a:t>（qwen3.5-flash）</a:t>
           </a:r>
-          <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1100"/>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -2275,9 +3654,15 @@
       <xdr:row>18</xdr:row>
       <xdr:rowOff>69850</xdr:rowOff>
     </xdr:to>
-    <xdr:sp>
+    <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="9" name="圆角矩形 8"/>
+        <xdr:cNvPr id="9" name="圆角矩形 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000009000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -2307,15 +3692,6 @@
           </a:gsLst>
           <a:lin ang="5400000" scaled="1"/>
         </a:gradFill>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
       </xdr:spPr>
       <xdr:style>
         <a:lnRef idx="2">
@@ -2444,7 +3820,6 @@
             <a:rPr lang="en-US" altLang="zh-CN" sz="1100"/>
             <a:t>LLM</a:t>
           </a:r>
-          <a:endParaRPr lang="en-US" altLang="zh-CN" sz="1100"/>
         </a:p>
         <a:p>
           <a:pPr algn="ctr"/>
@@ -2452,7 +3827,6 @@
             <a:rPr lang="zh-CN" altLang="en-US" sz="1100"/>
             <a:t>（text-embedding-v4）</a:t>
           </a:r>
-          <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1100"/>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -2471,9 +3845,15 @@
       <xdr:row>10</xdr:row>
       <xdr:rowOff>146050</xdr:rowOff>
     </xdr:to>
-    <xdr:cxnSp>
+    <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="10" name="直接连接符 9"/>
+        <xdr:cNvPr id="10" name="直接连接符 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000A000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvCxnSpPr>
           <a:stCxn id="3" idx="2"/>
           <a:endCxn id="4" idx="0"/>
@@ -2522,9 +3902,15 @@
       <xdr:row>12</xdr:row>
       <xdr:rowOff>69850</xdr:rowOff>
     </xdr:to>
-    <xdr:cxnSp>
+    <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="11" name="直接连接符 10"/>
+        <xdr:cNvPr id="11" name="直接连接符 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000B000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvCxnSpPr>
           <a:stCxn id="4" idx="3"/>
           <a:endCxn id="5" idx="1"/>
@@ -2573,9 +3959,15 @@
       <xdr:row>14</xdr:row>
       <xdr:rowOff>171450</xdr:rowOff>
     </xdr:to>
-    <xdr:cxnSp>
+    <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="13" name="肘形连接符 12"/>
+        <xdr:cNvPr id="13" name="肘形连接符 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000D000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvCxnSpPr>
           <a:stCxn id="2" idx="3"/>
           <a:endCxn id="9" idx="0"/>
@@ -2623,9 +4015,15 @@
       <xdr:row>32</xdr:row>
       <xdr:rowOff>25400</xdr:rowOff>
     </xdr:to>
-    <xdr:sp>
+    <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="17" name="圆角矩形 16"/>
+        <xdr:cNvPr id="17" name="圆角矩形 16">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000011000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -2655,15 +4053,6 @@
           </a:gsLst>
           <a:lin ang="5400000" scaled="1"/>
         </a:gradFill>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
       </xdr:spPr>
       <xdr:style>
         <a:lnRef idx="2">
@@ -2788,7 +4177,6 @@
             <a:rPr lang="en-US" altLang="zh-CN" sz="1100"/>
             <a:t>rag LLM</a:t>
           </a:r>
-          <a:endParaRPr lang="en-US" altLang="zh-CN" sz="1100"/>
         </a:p>
         <a:p>
           <a:pPr algn="ctr"/>
@@ -2796,7 +4184,6 @@
             <a:rPr lang="zh-CN" altLang="en-US" sz="1100"/>
             <a:t>（qwen-plus）</a:t>
           </a:r>
-          <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1100"/>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -2815,9 +4202,15 @@
       <xdr:row>29</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
-    <xdr:cxnSp>
+    <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="18" name="直接连接符 17"/>
+        <xdr:cNvPr id="18" name="直接连接符 17">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000012000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvCxnSpPr>
           <a:stCxn id="4" idx="2"/>
           <a:endCxn id="17" idx="0"/>
@@ -2865,9 +4258,15 @@
       <xdr:row>12</xdr:row>
       <xdr:rowOff>82550</xdr:rowOff>
     </xdr:to>
-    <xdr:cxnSp>
+    <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="19" name="直接连接符 18"/>
+        <xdr:cNvPr id="19" name="直接连接符 18">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000013000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvCxnSpPr>
           <a:stCxn id="20" idx="3"/>
           <a:endCxn id="4" idx="1"/>
@@ -2916,9 +4315,15 @@
       <xdr:row>14</xdr:row>
       <xdr:rowOff>6350</xdr:rowOff>
     </xdr:to>
-    <xdr:sp>
+    <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="20" name="圆角矩形 19"/>
+        <xdr:cNvPr id="20" name="圆角矩形 19">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000014000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -2948,15 +4353,6 @@
           </a:gsLst>
           <a:lin ang="5400000" scaled="1"/>
         </a:gradFill>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
       </xdr:spPr>
       <xdr:style>
         <a:lnRef idx="2">
@@ -3081,7 +4477,6 @@
             <a:rPr lang="zh-CN" altLang="en-US" sz="1100"/>
             <a:t>融合检索器</a:t>
           </a:r>
-          <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1100"/>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -3100,9 +4495,15 @@
       <xdr:row>23</xdr:row>
       <xdr:rowOff>146050</xdr:rowOff>
     </xdr:to>
-    <xdr:cxnSp>
+    <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="21" name="肘形连接符 20"/>
+        <xdr:cNvPr id="21" name="肘形连接符 20">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000015000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvCxnSpPr>
           <a:stCxn id="20" idx="1"/>
           <a:endCxn id="7" idx="3"/>
@@ -3152,9 +4553,15 @@
       <xdr:row>23</xdr:row>
       <xdr:rowOff>149860</xdr:rowOff>
     </xdr:to>
-    <xdr:cxnSp>
+    <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="22" name="直接连接符 21"/>
+        <xdr:cNvPr id="22" name="直接连接符 21">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000016000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvCxnSpPr>
           <a:stCxn id="7" idx="1"/>
           <a:endCxn id="6" idx="3"/>
@@ -3202,9 +4609,15 @@
       <xdr:row>22</xdr:row>
       <xdr:rowOff>25400</xdr:rowOff>
     </xdr:to>
-    <xdr:cxnSp>
+    <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="23" name="肘形连接符 22"/>
+        <xdr:cNvPr id="23" name="肘形连接符 22">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000017000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvCxnSpPr>
           <a:stCxn id="20" idx="1"/>
           <a:endCxn id="6" idx="0"/>
@@ -3252,9 +4665,15 @@
       <xdr:row>12</xdr:row>
       <xdr:rowOff>12700</xdr:rowOff>
     </xdr:to>
-    <xdr:sp>
+    <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="24" name="文本框 23"/>
+        <xdr:cNvPr id="24" name="文本框 23">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000018000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1"/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -3294,6 +4713,7 @@
         <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t">
           <a:noAutofit/>
         </a:bodyPr>
+        <a:lstStyle/>
         <a:p>
           <a:pPr algn="l"/>
           <a:r>
@@ -3304,7 +4724,6 @@
             <a:rPr lang="zh-CN" altLang="en-US" sz="1100"/>
             <a:t>检索</a:t>
           </a:r>
-          <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1100"/>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -3323,9 +4742,15 @@
       <xdr:row>19</xdr:row>
       <xdr:rowOff>152400</xdr:rowOff>
     </xdr:to>
-    <xdr:sp>
+    <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="25" name="文本框 24"/>
+        <xdr:cNvPr id="25" name="文本框 24">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000019000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1"/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -3474,7 +4899,6 @@
             <a:rPr lang="zh-CN" altLang="en-US" sz="1100"/>
             <a:t>子检索</a:t>
           </a:r>
-          <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1100"/>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -3493,9 +4917,15 @@
       <xdr:row>25</xdr:row>
       <xdr:rowOff>139700</xdr:rowOff>
     </xdr:to>
-    <xdr:sp>
+    <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="26" name="文本框 25"/>
+        <xdr:cNvPr id="26" name="文本框 25">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00001A000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1"/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -3644,7 +5074,6 @@
             <a:rPr lang="zh-CN" altLang="en-US" sz="1100"/>
             <a:t>父检索</a:t>
           </a:r>
-          <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1100"/>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -3663,9 +5092,15 @@
       <xdr:row>7</xdr:row>
       <xdr:rowOff>127000</xdr:rowOff>
     </xdr:to>
-    <xdr:sp>
+    <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="27" name="文本框 26"/>
+        <xdr:cNvPr id="27" name="文本框 26">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00001B000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1"/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -3814,7 +5249,6 @@
             <a:rPr lang="zh-CN" altLang="en-US" sz="1100"/>
             <a:t>用户输入</a:t>
           </a:r>
-          <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1100"/>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -3833,9 +5267,15 @@
       <xdr:row>11</xdr:row>
       <xdr:rowOff>178435</xdr:rowOff>
     </xdr:to>
-    <xdr:sp>
+    <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="28" name="文本框 27"/>
+        <xdr:cNvPr id="28" name="文本框 27">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00001C000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1"/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -3990,7 +5430,6 @@
             <a:rPr lang="zh-CN" altLang="en-US" sz="1100"/>
             <a:t>工具</a:t>
           </a:r>
-          <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1100"/>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -4009,9 +5448,15 @@
       <xdr:row>11</xdr:row>
       <xdr:rowOff>152400</xdr:rowOff>
     </xdr:to>
-    <xdr:sp>
+    <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="29" name="文本框 28"/>
+        <xdr:cNvPr id="29" name="文本框 28">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00001D000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1"/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -4158,7 +5603,6 @@
             <a:rPr lang="zh-CN" altLang="en-US" sz="1100"/>
             <a:t>调用工具，检索本地向量库</a:t>
           </a:r>
-          <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1100"/>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -4177,9 +5621,15 @@
       <xdr:row>30</xdr:row>
       <xdr:rowOff>100965</xdr:rowOff>
     </xdr:to>
-    <xdr:cxnSp>
+    <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="30" name="肘形连接符 29"/>
+        <xdr:cNvPr id="30" name="肘形连接符 29">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00001E000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvCxnSpPr>
           <a:stCxn id="6" idx="2"/>
           <a:endCxn id="31" idx="1"/>
@@ -4227,9 +5677,15 @@
       <xdr:row>32</xdr:row>
       <xdr:rowOff>25400</xdr:rowOff>
     </xdr:to>
-    <xdr:sp>
+    <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="31" name="圆角矩形 30"/>
+        <xdr:cNvPr id="31" name="圆角矩形 30">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00001F000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -4259,15 +5715,6 @@
           </a:gsLst>
           <a:lin ang="5400000" scaled="1"/>
         </a:gradFill>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
       </xdr:spPr>
       <xdr:style>
         <a:lnRef idx="2">
@@ -4396,7 +5843,6 @@
             <a:rPr lang="en-US" altLang="zh-CN" sz="1100"/>
             <a:t>LLM</a:t>
           </a:r>
-          <a:endParaRPr lang="en-US" altLang="zh-CN" sz="1100"/>
         </a:p>
         <a:p>
           <a:pPr algn="ctr"/>
@@ -4404,7 +5850,6 @@
             <a:rPr lang="zh-CN" altLang="en-US" sz="1100"/>
             <a:t>（qwen3-rerank）</a:t>
           </a:r>
-          <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1100"/>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -4423,9 +5868,15 @@
       <xdr:row>30</xdr:row>
       <xdr:rowOff>57150</xdr:rowOff>
     </xdr:to>
-    <xdr:sp>
+    <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="32" name="文本框 31"/>
+        <xdr:cNvPr id="32" name="文本框 31">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000020000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1"/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -4574,7 +6025,6 @@
             <a:rPr lang="zh-CN" altLang="en-US" sz="1100"/>
             <a:t>检索结果重排序</a:t>
           </a:r>
-          <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1100"/>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -4593,9 +6043,15 @@
       <xdr:row>30</xdr:row>
       <xdr:rowOff>104775</xdr:rowOff>
     </xdr:to>
-    <xdr:cxnSp>
+    <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="33" name="肘形连接符 32"/>
+        <xdr:cNvPr id="33" name="肘形连接符 32">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000021000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvCxnSpPr>
           <a:stCxn id="31" idx="3"/>
           <a:endCxn id="17" idx="1"/>
@@ -4643,9 +6099,15 @@
       <xdr:row>31</xdr:row>
       <xdr:rowOff>126365</xdr:rowOff>
     </xdr:to>
-    <xdr:sp>
+    <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="34" name="文本框 33"/>
+        <xdr:cNvPr id="34" name="文本框 33">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000022000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1"/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -4815,9 +6277,15 @@
       <xdr:row>24</xdr:row>
       <xdr:rowOff>152400</xdr:rowOff>
     </xdr:to>
-    <xdr:sp>
+    <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="35" name="文本框 34"/>
+        <xdr:cNvPr id="35" name="文本框 34">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000023000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1"/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -4987,9 +6455,15 @@
       <xdr:row>7</xdr:row>
       <xdr:rowOff>139700</xdr:rowOff>
     </xdr:to>
-    <xdr:sp>
+    <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="36" name="文本框 35"/>
+        <xdr:cNvPr id="36" name="文本框 35">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000024000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1"/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -5138,7 +6612,6 @@
             <a:rPr lang="zh-CN" altLang="en-US" sz="1100"/>
             <a:t>输出答案</a:t>
           </a:r>
-          <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1100"/>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -5157,9 +6630,15 @@
       <xdr:row>22</xdr:row>
       <xdr:rowOff>44450</xdr:rowOff>
     </xdr:to>
-    <xdr:cxnSp>
+    <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="37" name="直接连接符 36"/>
+        <xdr:cNvPr id="37" name="直接连接符 36">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000025000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvCxnSpPr>
           <a:stCxn id="7" idx="0"/>
           <a:endCxn id="9" idx="2"/>
@@ -5208,9 +6687,15 @@
       <xdr:row>23</xdr:row>
       <xdr:rowOff>149860</xdr:rowOff>
     </xdr:to>
-    <xdr:cxnSp>
+    <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="38" name="肘形连接符 37"/>
+        <xdr:cNvPr id="38" name="肘形连接符 37">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000026000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvCxnSpPr>
           <a:stCxn id="2" idx="1"/>
           <a:endCxn id="6" idx="1"/>
@@ -5260,9 +6745,15 @@
       <xdr:row>14</xdr:row>
       <xdr:rowOff>43180</xdr:rowOff>
     </xdr:to>
-    <xdr:sp>
+    <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="39" name="文本框 38"/>
+        <xdr:cNvPr id="39" name="文本框 38">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000027000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1"/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -5432,9 +6923,15 @@
       <xdr:row>10</xdr:row>
       <xdr:rowOff>62230</xdr:rowOff>
     </xdr:to>
-    <xdr:sp>
+    <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="40" name="文本框 39"/>
+        <xdr:cNvPr id="40" name="文本框 39">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000028000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1"/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -5586,8 +7083,8 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>9</xdr:col>
@@ -5601,9 +7098,15 @@
       <xdr:row>6</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
-    <xdr:sp>
+    <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="2" name="圆角矩形 1"/>
+        <xdr:cNvPr id="2" name="圆角矩形 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -5633,15 +7136,6 @@
           </a:gsLst>
           <a:lin ang="5400000" scaled="1"/>
         </a:gradFill>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
       </xdr:spPr>
       <xdr:style>
         <a:lnRef idx="2">
@@ -5785,9 +7279,15 @@
       <xdr:row>14</xdr:row>
       <xdr:rowOff>107950</xdr:rowOff>
     </xdr:to>
-    <xdr:sp>
+    <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="3" name="圆角矩形 2"/>
+        <xdr:cNvPr id="3" name="圆角矩形 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000003000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -5817,15 +7317,6 @@
           </a:gsLst>
           <a:lin ang="5400000" scaled="1"/>
         </a:gradFill>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
       </xdr:spPr>
       <xdr:style>
         <a:lnRef idx="2">
@@ -5969,9 +7460,15 @@
       <xdr:row>19</xdr:row>
       <xdr:rowOff>63500</xdr:rowOff>
     </xdr:to>
-    <xdr:sp>
+    <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="4" name="圆角矩形 3"/>
+        <xdr:cNvPr id="4" name="圆角矩形 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000004000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -6001,15 +7498,6 @@
           </a:gsLst>
           <a:lin ang="5400000" scaled="1"/>
         </a:gradFill>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
       </xdr:spPr>
       <xdr:style>
         <a:lnRef idx="2">
@@ -6153,9 +7641,15 @@
       <xdr:row>22</xdr:row>
       <xdr:rowOff>31750</xdr:rowOff>
     </xdr:to>
-    <xdr:sp>
+    <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="5" name="圆角矩形 4"/>
+        <xdr:cNvPr id="5" name="圆角矩形 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000005000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -6185,15 +7679,6 @@
           </a:gsLst>
           <a:lin ang="5400000" scaled="1"/>
         </a:gradFill>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
       </xdr:spPr>
       <xdr:style>
         <a:lnRef idx="2">
@@ -6337,9 +7822,15 @@
       <xdr:row>14</xdr:row>
       <xdr:rowOff>107950</xdr:rowOff>
     </xdr:to>
-    <xdr:sp>
+    <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="6" name="圆角矩形 5"/>
+        <xdr:cNvPr id="6" name="圆角矩形 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000006000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -6369,15 +7860,6 @@
           </a:gsLst>
           <a:lin ang="5400000" scaled="1"/>
         </a:gradFill>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
       </xdr:spPr>
       <xdr:style>
         <a:lnRef idx="2">
@@ -6521,9 +8003,15 @@
       <xdr:row>20</xdr:row>
       <xdr:rowOff>38100</xdr:rowOff>
     </xdr:to>
-    <xdr:sp>
+    <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="7" name="圆角矩形 6"/>
+        <xdr:cNvPr id="7" name="圆角矩形 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000007000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -6553,15 +8041,6 @@
           </a:gsLst>
           <a:lin ang="5400000" scaled="1"/>
         </a:gradFill>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
       </xdr:spPr>
       <xdr:style>
         <a:lnRef idx="2">
@@ -6705,9 +8184,15 @@
       <xdr:row>21</xdr:row>
       <xdr:rowOff>57150</xdr:rowOff>
     </xdr:to>
-    <xdr:sp>
+    <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="8" name="圆角矩形 7"/>
+        <xdr:cNvPr id="8" name="圆角矩形 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000008000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -6737,15 +8222,6 @@
           </a:gsLst>
           <a:lin ang="5400000" scaled="1"/>
         </a:gradFill>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
       </xdr:spPr>
       <xdr:style>
         <a:lnRef idx="2">
@@ -6889,9 +8365,15 @@
       <xdr:row>11</xdr:row>
       <xdr:rowOff>82550</xdr:rowOff>
     </xdr:to>
-    <xdr:cxnSp>
+    <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="9" name="曲线连接符 8"/>
+        <xdr:cNvPr id="9" name="曲线连接符 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000009000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvCxnSpPr>
           <a:stCxn id="2" idx="1"/>
           <a:endCxn id="3" idx="0"/>
@@ -6939,9 +8421,15 @@
       <xdr:row>16</xdr:row>
       <xdr:rowOff>38100</xdr:rowOff>
     </xdr:to>
-    <xdr:cxnSp>
+    <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="10" name="曲线连接符 9"/>
+        <xdr:cNvPr id="10" name="曲线连接符 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00000A000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvCxnSpPr>
           <a:stCxn id="3" idx="1"/>
           <a:endCxn id="4" idx="0"/>
@@ -6989,9 +8477,15 @@
       <xdr:row>19</xdr:row>
       <xdr:rowOff>6350</xdr:rowOff>
     </xdr:to>
-    <xdr:cxnSp>
+    <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="11" name="曲线连接符 10"/>
+        <xdr:cNvPr id="11" name="曲线连接符 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00000B000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvCxnSpPr>
           <a:stCxn id="4" idx="3"/>
           <a:endCxn id="5" idx="0"/>
@@ -7039,9 +8533,15 @@
       <xdr:row>26</xdr:row>
       <xdr:rowOff>88900</xdr:rowOff>
     </xdr:to>
-    <xdr:sp>
+    <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="12" name="圆角矩形 11"/>
+        <xdr:cNvPr id="12" name="圆角矩形 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00000C000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -7071,15 +8571,6 @@
           </a:gsLst>
           <a:lin ang="5400000" scaled="1"/>
         </a:gradFill>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
       </xdr:spPr>
       <xdr:style>
         <a:lnRef idx="2">
@@ -7223,9 +8714,15 @@
       <xdr:row>26</xdr:row>
       <xdr:rowOff>38100</xdr:rowOff>
     </xdr:to>
-    <xdr:sp>
+    <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="13" name="圆角矩形 12"/>
+        <xdr:cNvPr id="13" name="圆角矩形 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00000D000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -7255,15 +8752,6 @@
           </a:gsLst>
           <a:lin ang="5400000" scaled="1"/>
         </a:gradFill>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
       </xdr:spPr>
       <xdr:style>
         <a:lnRef idx="2">
@@ -7407,9 +8895,15 @@
       <xdr:row>22</xdr:row>
       <xdr:rowOff>31750</xdr:rowOff>
     </xdr:to>
-    <xdr:cxnSp>
+    <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="14" name="曲线连接符 13"/>
+        <xdr:cNvPr id="14" name="曲线连接符 13">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00000E000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvCxnSpPr>
           <a:stCxn id="5" idx="2"/>
           <a:endCxn id="4" idx="2"/>
@@ -7459,9 +8953,15 @@
       <xdr:row>24</xdr:row>
       <xdr:rowOff>165100</xdr:rowOff>
     </xdr:to>
-    <xdr:cxnSp>
+    <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="15" name="曲线连接符 14"/>
+        <xdr:cNvPr id="15" name="曲线连接符 14">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00000F000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvCxnSpPr>
           <a:stCxn id="4" idx="1"/>
           <a:endCxn id="12" idx="1"/>
@@ -7511,9 +9011,15 @@
       <xdr:row>20</xdr:row>
       <xdr:rowOff>107950</xdr:rowOff>
     </xdr:to>
-    <xdr:cxnSp>
+    <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="16" name="曲线连接符 15"/>
+        <xdr:cNvPr id="16" name="曲线连接符 15">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000010000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvCxnSpPr>
           <a:stCxn id="5" idx="3"/>
           <a:endCxn id="6" idx="1"/>
@@ -7563,9 +9069,15 @@
       <xdr:row>32</xdr:row>
       <xdr:rowOff>88900</xdr:rowOff>
     </xdr:to>
-    <xdr:sp>
+    <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="17" name="圆角矩形 16"/>
+        <xdr:cNvPr id="17" name="圆角矩形 16">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000011000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -7595,15 +9107,6 @@
           </a:gsLst>
           <a:lin ang="5400000" scaled="1"/>
         </a:gradFill>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
       </xdr:spPr>
       <xdr:style>
         <a:lnRef idx="2">
@@ -7747,9 +9250,15 @@
       <xdr:row>11</xdr:row>
       <xdr:rowOff>82550</xdr:rowOff>
     </xdr:to>
-    <xdr:cxnSp>
+    <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="18" name="曲线连接符 17"/>
+        <xdr:cNvPr id="18" name="曲线连接符 17">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000012000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvCxnSpPr>
           <a:stCxn id="2" idx="3"/>
           <a:endCxn id="6" idx="0"/>
@@ -7797,9 +9306,15 @@
       <xdr:row>6</xdr:row>
       <xdr:rowOff>25400</xdr:rowOff>
     </xdr:to>
-    <xdr:sp>
+    <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="19" name="文本框 18"/>
+        <xdr:cNvPr id="19" name="文本框 18">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000013000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1"/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -7839,13 +9354,13 @@
         <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t">
           <a:noAutofit/>
         </a:bodyPr>
+        <a:lstStyle/>
         <a:p>
           <a:pPr algn="l"/>
           <a:r>
             <a:rPr lang="zh-CN" altLang="en-US" sz="1100"/>
             <a:t>route_initial</a:t>
           </a:r>
-          <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1100"/>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -7864,9 +9379,15 @@
       <xdr:row>5</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
-    <xdr:sp>
+    <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="20" name="文本框 19"/>
+        <xdr:cNvPr id="20" name="文本框 19">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000014000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1"/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -8011,7 +9532,6 @@
             <a:rPr lang="zh-CN" altLang="en-US" sz="1100"/>
             <a:t>route_initial</a:t>
           </a:r>
-          <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1100"/>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -8030,9 +9550,15 @@
       <xdr:row>30</xdr:row>
       <xdr:rowOff>165100</xdr:rowOff>
     </xdr:to>
-    <xdr:cxnSp>
+    <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="21" name="曲线连接符 20"/>
+        <xdr:cNvPr id="21" name="曲线连接符 20">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000015000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvCxnSpPr>
           <a:stCxn id="12" idx="3"/>
           <a:endCxn id="17" idx="1"/>
@@ -8082,9 +9608,15 @@
       <xdr:row>30</xdr:row>
       <xdr:rowOff>165100</xdr:rowOff>
     </xdr:to>
-    <xdr:cxnSp>
+    <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="22" name="曲线连接符 21"/>
+        <xdr:cNvPr id="22" name="曲线连接符 21">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000016000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvCxnSpPr>
           <a:stCxn id="13" idx="1"/>
           <a:endCxn id="17" idx="3"/>
@@ -8134,9 +9666,15 @@
       <xdr:row>17</xdr:row>
       <xdr:rowOff>12700</xdr:rowOff>
     </xdr:to>
-    <xdr:cxnSp>
+    <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="23" name="曲线连接符 22"/>
+        <xdr:cNvPr id="23" name="曲线连接符 22">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000017000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvCxnSpPr>
           <a:stCxn id="6" idx="2"/>
           <a:endCxn id="7" idx="0"/>
@@ -8186,9 +9724,15 @@
       <xdr:row>18</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
-    <xdr:cxnSp>
+    <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="24" name="曲线连接符 23"/>
+        <xdr:cNvPr id="24" name="曲线连接符 23">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000018000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvCxnSpPr>
           <a:stCxn id="7" idx="1"/>
           <a:endCxn id="8" idx="0"/>
@@ -8239,9 +9783,15 @@
       <xdr:row>19</xdr:row>
       <xdr:rowOff>133350</xdr:rowOff>
     </xdr:to>
-    <xdr:cxnSp>
+    <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="25" name="曲线连接符 24"/>
+        <xdr:cNvPr id="25" name="曲线连接符 24">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000019000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvCxnSpPr>
           <a:stCxn id="8" idx="1"/>
           <a:endCxn id="3" idx="3"/>
@@ -8291,9 +9841,15 @@
       <xdr:row>20</xdr:row>
       <xdr:rowOff>38100</xdr:rowOff>
     </xdr:to>
-    <xdr:cxnSp>
+    <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="26" name="曲线连接符 25"/>
+        <xdr:cNvPr id="26" name="曲线连接符 25">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00001A000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvCxnSpPr>
           <a:stCxn id="8" idx="3"/>
           <a:endCxn id="7" idx="2"/>
@@ -8344,9 +9900,15 @@
       <xdr:row>24</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
-    <xdr:cxnSp>
+    <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="27" name="曲线连接符 26"/>
+        <xdr:cNvPr id="27" name="曲线连接符 26">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00001B000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvCxnSpPr>
           <a:stCxn id="7" idx="3"/>
           <a:endCxn id="13" idx="3"/>
@@ -8396,9 +9958,15 @@
       <xdr:row>21</xdr:row>
       <xdr:rowOff>50800</xdr:rowOff>
     </xdr:to>
-    <xdr:sp>
+    <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="28" name="文本框 27"/>
+        <xdr:cNvPr id="28" name="文本框 27">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00001C000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1"/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -8541,7 +10109,6 @@
             <a:rPr lang="zh-CN" altLang="en-US" sz="1100"/>
             <a:t>transfer_to_code_agent</a:t>
           </a:r>
-          <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1100"/>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -8560,9 +10127,15 @@
       <xdr:row>20</xdr:row>
       <xdr:rowOff>107950</xdr:rowOff>
     </xdr:to>
-    <xdr:sp>
+    <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="29" name="文本框 28"/>
+        <xdr:cNvPr id="29" name="文本框 28">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00001D000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1"/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -8705,7 +10278,6 @@
             <a:rPr lang="zh-CN" altLang="en-US" sz="1100"/>
             <a:t>transfer_to_main_agent</a:t>
           </a:r>
-          <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1100"/>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -8958,28 +10530,226 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04781AB3-3953-48A9-9F20-0A67D4E17E98}">
+  <dimension ref="C54:P79"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="16384" width="8.7265625" style="10"/>
+  </cols>
+  <sheetData>
+    <row r="54" spans="3:16" x14ac:dyDescent="0.25">
+      <c r="C54" s="10" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="55" spans="3:16" x14ac:dyDescent="0.25">
+      <c r="D55" s="11" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="56" spans="3:16" x14ac:dyDescent="0.25">
+      <c r="D56" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="G56" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="M56" s="10" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="57" spans="3:16" x14ac:dyDescent="0.25">
+      <c r="D57" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="M57" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="O57" s="10" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="58" spans="3:16" x14ac:dyDescent="0.25">
+      <c r="D58" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="M58" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="O58" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="P58" s="10" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="59" spans="3:16" x14ac:dyDescent="0.25">
+      <c r="D59" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="M59" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="O59" s="10" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="60" spans="3:16" x14ac:dyDescent="0.25">
+      <c r="D60" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="M60" s="10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="61" spans="3:16" x14ac:dyDescent="0.25">
+      <c r="D61" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="M61" s="10" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="62" spans="3:16" x14ac:dyDescent="0.25">
+      <c r="D62" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="M62" s="10" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="63" spans="3:16" x14ac:dyDescent="0.25">
+      <c r="D63" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="M63" s="10" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="64" spans="3:16" x14ac:dyDescent="0.25">
+      <c r="D64" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="M64" s="10" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="65" spans="13:14" x14ac:dyDescent="0.25">
+      <c r="M65" s="10" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="66" spans="13:14" x14ac:dyDescent="0.25">
+      <c r="M66" s="10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="67" spans="13:14" x14ac:dyDescent="0.25">
+      <c r="M67" s="10" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="68" spans="13:14" x14ac:dyDescent="0.25">
+      <c r="M68" s="10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="70" spans="13:14" x14ac:dyDescent="0.25">
+      <c r="N70" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="71" spans="13:14" x14ac:dyDescent="0.25">
+      <c r="N71" s="10" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="72" spans="13:14" x14ac:dyDescent="0.25">
+      <c r="N72" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="73" spans="13:14" x14ac:dyDescent="0.25">
+      <c r="M73" s="10" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="74" spans="13:14" x14ac:dyDescent="0.25">
+      <c r="N74" s="10" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="75" spans="13:14" x14ac:dyDescent="0.25">
+      <c r="N75" s="10" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="77" spans="13:14" x14ac:dyDescent="0.25">
+      <c r="M77" s="10" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="78" spans="13:14" x14ac:dyDescent="0.25">
+      <c r="N78" s="10" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="79" spans="13:14" x14ac:dyDescent="0.25">
+      <c r="N79" s="10" t="s">
+        <v>26</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3FDE77DA-E28E-413E-9F2F-D98C7C60CCB7}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <sheetData/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB92047D-8639-43FD-A93F-5B045E1E2272}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="B8:T27"/>
-  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="8" spans="2:20">
+    <row r="8" spans="2:20" x14ac:dyDescent="0.25">
       <c r="C8" s="1" t="s">
         <v>0</v>
       </c>
@@ -8987,8 +10757,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" ht="14.75"/>
-    <row r="10" spans="2:20">
+    <row r="10" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B10" s="2"/>
       <c r="C10" s="3"/>
       <c r="D10" s="3"/>
@@ -9004,103 +10773,103 @@
       <c r="S10" s="3"/>
       <c r="T10" s="4"/>
     </row>
-    <row r="11" spans="2:20">
+    <row r="11" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B11" s="5"/>
       <c r="H11" s="6"/>
       <c r="N11" s="5"/>
       <c r="T11" s="6"/>
     </row>
-    <row r="12" spans="2:20">
+    <row r="12" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B12" s="5"/>
       <c r="H12" s="6"/>
       <c r="N12" s="5"/>
       <c r="T12" s="6"/>
     </row>
-    <row r="13" spans="2:20">
+    <row r="13" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B13" s="5"/>
       <c r="H13" s="6"/>
       <c r="N13" s="5"/>
       <c r="T13" s="6"/>
     </row>
-    <row r="14" spans="2:20">
+    <row r="14" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B14" s="5"/>
       <c r="H14" s="6"/>
       <c r="N14" s="5"/>
       <c r="T14" s="6"/>
     </row>
-    <row r="15" spans="2:20">
+    <row r="15" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B15" s="5"/>
       <c r="H15" s="6"/>
       <c r="N15" s="5"/>
       <c r="T15" s="6"/>
     </row>
-    <row r="16" spans="2:20">
+    <row r="16" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B16" s="5"/>
       <c r="H16" s="6"/>
       <c r="N16" s="5"/>
       <c r="T16" s="6"/>
     </row>
-    <row r="17" spans="2:20">
+    <row r="17" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B17" s="5"/>
       <c r="H17" s="6"/>
       <c r="N17" s="5"/>
       <c r="T17" s="6"/>
     </row>
-    <row r="18" spans="2:20">
+    <row r="18" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B18" s="5"/>
       <c r="H18" s="6"/>
       <c r="N18" s="5"/>
       <c r="T18" s="6"/>
     </row>
-    <row r="19" spans="2:20">
+    <row r="19" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B19" s="5"/>
       <c r="H19" s="6"/>
       <c r="N19" s="5"/>
       <c r="T19" s="6"/>
     </row>
-    <row r="20" spans="2:20">
+    <row r="20" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B20" s="5"/>
       <c r="H20" s="6"/>
       <c r="N20" s="5"/>
       <c r="T20" s="6"/>
     </row>
-    <row r="21" spans="2:20">
+    <row r="21" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B21" s="5"/>
       <c r="H21" s="6"/>
       <c r="N21" s="5"/>
       <c r="T21" s="6"/>
     </row>
-    <row r="22" spans="2:20">
+    <row r="22" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B22" s="5"/>
       <c r="H22" s="6"/>
       <c r="N22" s="5"/>
       <c r="T22" s="6"/>
     </row>
-    <row r="23" spans="2:20">
+    <row r="23" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B23" s="5"/>
       <c r="H23" s="6"/>
       <c r="N23" s="5"/>
       <c r="T23" s="6"/>
     </row>
-    <row r="24" spans="2:20">
+    <row r="24" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B24" s="5"/>
       <c r="H24" s="6"/>
       <c r="N24" s="5"/>
       <c r="T24" s="6"/>
     </row>
-    <row r="25" spans="2:20">
+    <row r="25" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B25" s="5"/>
       <c r="H25" s="6"/>
       <c r="N25" s="5"/>
       <c r="T25" s="6"/>
     </row>
-    <row r="26" spans="2:20">
+    <row r="26" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B26" s="5"/>
       <c r="H26" s="6"/>
       <c r="N26" s="5"/>
       <c r="T26" s="6"/>
     </row>
-    <row r="27" ht="14.75" spans="2:20">
+    <row r="27" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B27" s="7"/>
       <c r="C27" s="8"/>
       <c r="D27" s="8"/>
@@ -9117,8 +10886,8 @@
       <c r="T27" s="9"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>